--- a/store/May-2026/Mail Attachment/Non_BTC_Report_31-May-2026.xlsx
+++ b/store/May-2026/Mail Attachment/Non_BTC_Report_31-May-2026.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
